--- a/artfynd/A 58082-2022 artfynd.xlsx
+++ b/artfynd/A 58082-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58082-2022 artfynd.xlsx
+++ b/artfynd/A 58082-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89600726</v>
+        <v>89600768</v>
       </c>
       <c r="B2" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404387.0368101947</v>
+        <v>404498</v>
       </c>
       <c r="R2" t="n">
-        <v>7064044.963414576</v>
+        <v>7064592</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,14 @@
           <t>2020-09-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89600768</v>
+        <v>107258607</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,16 +810,20 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bränthön, Jmt</t>
+          <t>Stortjärnen Juvuln Åre, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404497.8068570454</v>
+        <v>404756</v>
       </c>
       <c r="R3" t="n">
-        <v>7064591.99351103</v>
+        <v>7063765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,27 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,31 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107258609</v>
+        <v>107258608</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,7 +918,11 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404422.239326037</v>
+        <v>404465</v>
       </c>
       <c r="R4" t="n">
-        <v>7064517.941830191</v>
+        <v>7064504</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,19 +963,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1033,15 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107258610</v>
+        <v>107258609</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404455.1293754542</v>
+        <v>404422</v>
       </c>
       <c r="R5" t="n">
-        <v>7064591.508950029</v>
+        <v>7064518</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,19 +1069,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1154,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107258607</v>
+        <v>107258610</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>404755.5111078721</v>
+        <v>404455</v>
       </c>
       <c r="R6" t="n">
-        <v>7063764.822795196</v>
+        <v>7064591</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,19 +1175,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1278,12 +1212,7 @@
         <v>107258628</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404588.0690095468</v>
+        <v>404588</v>
       </c>
       <c r="R7" t="n">
-        <v>7064520.029476826</v>
+        <v>7064520</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,19 +1281,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1396,58 +1315,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107258608</v>
+        <v>89600726</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220686</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stortjärnen Juvuln Åre, Jmt</t>
+          <t>Bränthön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404465.3900776547</v>
+        <v>404387</v>
       </c>
       <c r="R8" t="n">
-        <v>7064504.653031247</v>
+        <v>7064045</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,27 +1380,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,15 +1400,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58082-2022 artfynd.xlsx
+++ b/artfynd/A 58082-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600768</t>
         </is>
       </c>
     </row>
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258607</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258608</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258609</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258610</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258628</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,8 +1448,22 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600726</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>